--- a/KIT-REPRISE/07-plan-actions.xlsx
+++ b/KIT-REPRISE/07-plan-actions.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,17 +438,29 @@
       <c r="L1" t="str">
         <v>Date de création</v>
       </c>
+      <c r="M1" t="str">
+        <v>Efficacité</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Efficacité vérifiée le</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Vérifiée par</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Constat d'efficacité</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:P4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -487,6 +499,18 @@
       <c r="L1" t="str">
         <v>Date de création</v>
       </c>
+      <c r="M1" t="str">
+        <v>Efficacité</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Efficacité vérifiée le</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Vérifiée par</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Constat d'efficacité</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -525,6 +549,18 @@
       <c r="L2" t="str">
         <v>2026-09-01</v>
       </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -563,17 +599,79 @@
       <c r="L3" t="str">
         <v>2026-09-01</v>
       </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>pa-3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Poser une main courante dans l'escalier B</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Main courante des deux côtés</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Ville</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Patrimoine Bâti</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Chute de hauteur</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Manuel</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Régie bâtiment</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Haute</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Fait</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Efficace</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Préventeur</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Aucune chute ni glissade signalée depuis la pose</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -678,7 +776,7 @@
         <v>Texte</v>
       </c>
       <c r="D6" t="str">
-        <v>Voirie &amp; Réseaux · Collecte &amp; Propreté</v>
+        <v>Voirie &amp; Réseaux · Collecte &amp; Propreté · Patrimoine Bâti</v>
       </c>
       <c r="E6" t="str">
         <v>texte libre — reprendre exactement un service des référentiels (Administration → Référentiels)</v>
@@ -780,7 +878,7 @@
         <v>Texte</v>
       </c>
       <c r="D12" t="str">
-        <v>En cours · À faire</v>
+        <v>En cours · À faire · Fait</v>
       </c>
       <c r="E12" t="str">
         <v>liste : une valeur inconnue est remplacée par « À faire »</v>
@@ -803,9 +901,77 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Efficacité</v>
+      </c>
+      <c r="B14" t="str">
+        <v>non</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Efficace · Non efficace</v>
+      </c>
+      <c r="E14" t="str">
+        <v>liste : une valeur inconnue est laissée vide</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Efficacité vérifiée le</v>
+      </c>
+      <c r="B15" t="str">
+        <v>non</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Date AAAA-MM-JJ (une date Excel convient aussi)</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Vérifiée par</v>
+      </c>
+      <c r="B16" t="str">
+        <v>non</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Constat d'efficacité</v>
+      </c>
+      <c r="B17" t="str">
+        <v>non</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>